--- a/templates/物资交换作业单模板_exchange_worksheet_template.xlsx
+++ b/templates/物资交换作业单模板_exchange_worksheet_template.xlsx
@@ -61,11 +61,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
